--- a/reports/ibis_files/hark_lfd2nx_ami_rx/hark_lfd2nx_ami_rx.xlsx
+++ b/reports/ibis_files/hark_lfd2nx_ami_rx/hark_lfd2nx_ami_rx.xlsx
@@ -114,7 +114,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09T23:35:23-05:00</t>
+          <t>2026-06-12T22:46:18-05:00</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.2.1</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -264,8 +264,10 @@
           <t>Errors</t>
         </is>
       </c>
-      <c r="B16">
-        <v>0</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -274,8 +276,10 @@
           <t>Warnings</t>
         </is>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -284,8 +288,10 @@
           <t>Cautions</t>
         </is>
       </c>
-      <c r="B18">
-        <v>0</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -296,7 +302,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -327,7 +333,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -347,7 +353,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -357,7 +363,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -421,14 +427,14 @@
           <t>IBIS file passes IBISCHK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="D31" t="inlineStr" s="6">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PASS=3. No existing '|IQ Score:' tag found inside the .ibs file. This is reported as a writeback note only; it does not fail the quality check because this tool is intended to help assign the score. | IBISCHK version not found documented inside the .ibs file. This is reported as a documentation note only; it does not block Level 1. | IBISCHK: 0 errors, 0 warning(s): IBISCHK path: C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t>WARN=1, PASS=2. No existing '|IQ Score:' tag found inside the .ibs file. This is reported as a writeback note only; it does not fail the quality check because this tool is intended to help assign the score. | IBISCHK version not found documented inside the .ibs file. This is reported as a documentation note only; it does not block Level 1. | IBISCHK not found on PATH — skipping execution check. Install IBISCHK and ensure it is on PATH</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2.1-file-lfd2nx_ami_rx.ibs-4440a0c08394</t>
+          <t>2.1-file-lfd2nx_ami_rx.ibs-3009dd261eec</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3716,7 +3722,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2.1-file-lfd2nx_ami_rx.ibs-a110ca3a10cd</t>
+          <t>2.1-file-lfd2nx_ami_rx.ibs-3009dd261eec-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3783,7 +3789,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.1-file-lfd2nx_ami_rx.ibs-ae0380173cdf</t>
+          <t>2.1-file-lfd2nx_ami_rx.ibs-3009dd261eec-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3801,14 +3807,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E4" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3838,19 +3844,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>IBISCHK: 0 errors, 0 warning(s)</t>
+          <t>IBISCHK not found on PATH — skipping execution check. Install IBISCHK and ensure it is on PATH.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>IBISCHK path: C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3.1.1-component-lfd2nx_Serdes_Rx-cc61d09592b9</t>
+          <t>3.1.1-component-lfd2nx_Serdes_Rx-de68c89d6532</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3917,7 +3923,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3.1.2-component-lfd2nx_Serdes_Rx-ecd707d242e4</t>
+          <t>3.1.2-component-lfd2nx_Serdes_Rx-9ffb1f074d3b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3984,7 +3990,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3.2.1-component-lfd2nx_Serdes_Rx-49981612c266</t>
+          <t>3.2.1-component-lfd2nx_Serdes_Rx-1ab54a2feed4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4051,7 +4057,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4.1-file-lfd2nx_ami_rx.ibs-5dd9a6977b1a</t>
+          <t>4.1-file-lfd2nx_ami_rx.ibs-1460ddaf9247</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4118,7 +4124,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3.2.2-component-lfd2nx_Serdes_Rx-f83bdc7d9514</t>
+          <t>3.2.2-component-lfd2nx_Serdes_Rx-45a6d5f7b46e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4186,7 +4192,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3.3.1-component-lfd2nx_Serdes_Rx-00fc3190912b</t>
+          <t>3.3.1-component-lfd2nx_Serdes_Rx-56f187e983e7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4253,7 +4259,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3.3.2-component-lfd2nx_Serdes_Rx-efc78ec00c6d</t>
+          <t>3.3.2-component-lfd2nx_Serdes_Rx-3f4f3afe23d5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4320,7 +4326,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5.1.1-model-lfd2nx_in-0b63040f3f37</t>
+          <t>5.1.1-model-lfd2nx_in-45bb2788d83e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4389,7 +4395,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5.2.6-model-lfd2nx_in-8a29ca8c8ecc</t>
+          <t>5.2.6-model-lfd2nx_in-729f7787eb55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4456,7 +4462,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5.2.8-model-lfd2nx_in-651323b32571</t>
+          <t>5.2.8-model-lfd2nx_in-cc92f419fe13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4523,7 +4529,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5.5.2-model-lfd2nx_in-9b256a3becb4</t>
+          <t>5.5.2-model-lfd2nx_in-a548daae8339</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4590,7 +4596,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5.1.2-model-lfd2nx_in-e03957b81a4a</t>
+          <t>5.1.2-model-lfd2nx_in-299a3eb77ba8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4657,7 +4663,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5.1.4-model-lfd2nx_in-ec368e2e3444</t>
+          <t>5.1.4-model-lfd2nx_in-423baf623553</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4728,7 +4734,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5.3.6-model-lfd2nx_in-0004caca1545</t>
+          <t>5.3.6-model-lfd2nx_in-652d0982bcd6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4795,7 +4801,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5.3.14-model-lfd2nx_in-969f5b8b0935</t>
+          <t>5.3.14-model-lfd2nx_in-4d4c3687e363</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4862,7 +4868,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5.3.10-model-lfd2nx_in-166dc43e1da9</t>
+          <t>5.3.10-model-lfd2nx_in-63aef794fe5f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4929,7 +4935,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5.4.1-model-lfd2nx_in-8f6aba38ff5b</t>
+          <t>5.4.1-model-lfd2nx_in-5bb4dadb9e62</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4996,7 +5002,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5.4.2-model-lfd2nx_in-2170f1048874</t>
+          <t>5.4.2-model-lfd2nx_in-9bcfdeb10522</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5063,7 +5069,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5.4.3-model-lfd2nx_in-c26a94713218</t>
+          <t>5.4.3-model-lfd2nx_in-2454c75d54a0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5130,7 +5136,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5.4.4-model-lfd2nx_in-37e54511e77a</t>
+          <t>5.4.4-model-lfd2nx_in-7dab5af2c8b9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5197,7 +5203,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5.5.4-model-lfd2nx_in-b5093e5e4f4c</t>
+          <t>5.5.4-model-lfd2nx_in-2a0e920cddbc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5264,7 +5270,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5.6.2-model-lfd2nx_in-4a3b42e08bb3</t>
+          <t>5.6.2-model-lfd2nx_in-16fa57e9a8ca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5331,7 +5337,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5.3.1-model-lfd2nx_in-aecc4252af07</t>
+          <t>5.3.1-model-lfd2nx_in-25a50501b3ce</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5398,7 +5404,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5.3.2-model-lfd2nx_in-72e66b21cbdb</t>
+          <t>5.3.2-model-lfd2nx_in-9818801b15b8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5465,7 +5471,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5.3.3-model-lfd2nx_in-8279e7d83c86</t>
+          <t>5.3.3-model-lfd2nx_in-fb1006256aab</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5532,7 +5538,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5.3.5-model-lfd2nx_in-06b926a63e27</t>
+          <t>5.3.5-model-lfd2nx_in-c12f12be04de</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5599,7 +5605,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5.3.7-model-lfd2nx_in-957abc6cacbd</t>
+          <t>5.3.7-model-lfd2nx_in-a5771ac32f97</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5666,7 +5672,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5.3.8-model-lfd2nx_in-d0b5006ac4b7</t>
+          <t>5.3.8-model-lfd2nx_in-6d8a25411316</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5733,7 +5739,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5.3.9-model-lfd2nx_in-7ad3672b84da</t>
+          <t>5.3.9-model-lfd2nx_in-0cca5230c221</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5792,6 +5798,73 @@
         </is>
       </c>
       <c r="M33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>5.9.1-model-lfd2nx_in-300cb0cf58d1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5.9.1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="7">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>lfd2nx_in</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Model_type=Input has no Pullup/Pulldown — Zout NA</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/reports/ibis_files/hark_lfd2nx_ami_rx/hark_lfd2nx_ami_rx.xlsx
+++ b/reports/ibis_files/hark_lfd2nx_ami_rx/hark_lfd2nx_ami_rx.xlsx
@@ -114,7 +114,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12T22:46:18-05:00</t>
+          <t>2026-06-13T23:04:06-05:00</t>
         </is>
       </c>
     </row>
